--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT_Projects\auto-counts-documents-and-product-number\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B4B119-349C-4F3A-8A5B-E84D24F49983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EFC819-57BE-481D-9AD5-739241EEB94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FDB848D0-7B59-4CCA-A254-3AF7A4F99E28}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>發票</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,6 +79,14 @@
   </si>
   <si>
     <t>詢價單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>採購單號:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{採購單號}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -300,7 +308,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -339,6 +347,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -654,103 +665,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C15AC15-1F57-44A7-9D83-DC83199CDC84}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:G10"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="3" width="10.77734375" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" customWidth="1"/>
+    <col min="3" max="4" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="2:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="1"/>
+      <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="2:7" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-    </row>
-    <row r="3" spans="1:3" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="F2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-    </row>
-    <row r="4" spans="1:3" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="10"/>
+    </row>
+    <row r="4" spans="2:7" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9">
-        <f t="shared" ref="B4:C5" si="0">B3</f>
+      <c r="C4" s="9">
+        <f t="shared" ref="C4:D4" si="0">C3</f>
         <v>0</v>
       </c>
-      <c r="C4" s="10">
+      <c r="D4" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="2:7" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-    </row>
-    <row r="6" spans="1:3" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+    </row>
+    <row r="6" spans="2:7" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="9">
+      <c r="C6" s="9">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="10">
         <v>1</v>
       </c>
-      <c r="C6" s="10">
+    </row>
+    <row r="7" spans="2:7" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="9">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="9">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="2:7" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-    </row>
-    <row r="9" spans="1:3" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" spans="2:7" ht="30.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-    </row>
-    <row r="10" spans="1:3" ht="30.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="2:7" ht="30.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="11" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>